--- a/feeds/0463_MM_feed.xlsx
+++ b/feeds/0463_MM_feed.xlsx
@@ -1406,12 +1406,28 @@
       <c r="DY2" t="inlineStr"/>
       <c r="DZ2" t="inlineStr"/>
       <c r="EA2" t="inlineStr"/>
-      <c r="EB2" t="inlineStr"/>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>133.99</t>
+        </is>
+      </c>
       <c r="EC2" t="inlineStr"/>
       <c r="ED2" t="inlineStr"/>
-      <c r="EE2" t="inlineStr"/>
-      <c r="EF2" t="inlineStr"/>
-      <c r="EG2" t="inlineStr"/>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="EH2" t="inlineStr"/>
       <c r="EI2" t="inlineStr"/>
       <c r="EJ2" t="inlineStr"/>
@@ -1664,12 +1680,28 @@
       <c r="DY3" t="inlineStr"/>
       <c r="DZ3" t="inlineStr"/>
       <c r="EA3" t="inlineStr"/>
-      <c r="EB3" t="inlineStr"/>
+      <c r="EB3" t="inlineStr">
+        <is>
+          <t>133.99</t>
+        </is>
+      </c>
       <c r="EC3" t="inlineStr"/>
       <c r="ED3" t="inlineStr"/>
-      <c r="EE3" t="inlineStr"/>
-      <c r="EF3" t="inlineStr"/>
-      <c r="EG3" t="inlineStr"/>
+      <c r="EE3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="EF3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="EG3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="EH3" t="inlineStr"/>
       <c r="EI3" t="inlineStr"/>
       <c r="EJ3" t="inlineStr"/>
@@ -1922,12 +1954,28 @@
       <c r="DY4" t="inlineStr"/>
       <c r="DZ4" t="inlineStr"/>
       <c r="EA4" t="inlineStr"/>
-      <c r="EB4" t="inlineStr"/>
+      <c r="EB4" t="inlineStr">
+        <is>
+          <t>133.99</t>
+        </is>
+      </c>
       <c r="EC4" t="inlineStr"/>
       <c r="ED4" t="inlineStr"/>
-      <c r="EE4" t="inlineStr"/>
-      <c r="EF4" t="inlineStr"/>
-      <c r="EG4" t="inlineStr"/>
+      <c r="EE4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="EF4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="EG4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="EH4" t="inlineStr"/>
       <c r="EI4" t="inlineStr"/>
       <c r="EJ4" t="inlineStr"/>
@@ -2180,12 +2228,28 @@
       <c r="DY5" t="inlineStr"/>
       <c r="DZ5" t="inlineStr"/>
       <c r="EA5" t="inlineStr"/>
-      <c r="EB5" t="inlineStr"/>
+      <c r="EB5" t="inlineStr">
+        <is>
+          <t>147.99</t>
+        </is>
+      </c>
       <c r="EC5" t="inlineStr"/>
       <c r="ED5" t="inlineStr"/>
-      <c r="EE5" t="inlineStr"/>
-      <c r="EF5" t="inlineStr"/>
-      <c r="EG5" t="inlineStr"/>
+      <c r="EE5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="EF5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="EG5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="EH5" t="inlineStr"/>
       <c r="EI5" t="inlineStr"/>
       <c r="EJ5" t="inlineStr"/>

--- a/feeds/0463_MM_feed.xlsx
+++ b/feeds/0463_MM_feed.xlsx
@@ -1428,19 +1428,31 @@
           <t>10</t>
         </is>
       </c>
-      <c r="EH2" t="inlineStr"/>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
       <c r="EI2" t="inlineStr"/>
       <c r="EJ2" t="inlineStr"/>
       <c r="EK2" t="inlineStr"/>
       <c r="EL2" t="inlineStr"/>
       <c r="EM2" t="inlineStr"/>
-      <c r="EN2" t="inlineStr"/>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>2#4</t>
+        </is>
+      </c>
       <c r="EO2" t="inlineStr"/>
       <c r="EP2" t="inlineStr"/>
       <c r="EQ2" t="inlineStr"/>
       <c r="ER2" t="inlineStr"/>
       <c r="ES2" t="inlineStr"/>
-      <c r="ET2" t="inlineStr"/>
+      <c r="ET2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1702,19 +1714,31 @@
           <t>10</t>
         </is>
       </c>
-      <c r="EH3" t="inlineStr"/>
+      <c r="EH3" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
       <c r="EI3" t="inlineStr"/>
       <c r="EJ3" t="inlineStr"/>
       <c r="EK3" t="inlineStr"/>
       <c r="EL3" t="inlineStr"/>
       <c r="EM3" t="inlineStr"/>
-      <c r="EN3" t="inlineStr"/>
+      <c r="EN3" t="inlineStr">
+        <is>
+          <t>2#4</t>
+        </is>
+      </c>
       <c r="EO3" t="inlineStr"/>
       <c r="EP3" t="inlineStr"/>
       <c r="EQ3" t="inlineStr"/>
       <c r="ER3" t="inlineStr"/>
       <c r="ES3" t="inlineStr"/>
-      <c r="ET3" t="inlineStr"/>
+      <c r="ET3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1976,19 +2000,31 @@
           <t>10</t>
         </is>
       </c>
-      <c r="EH4" t="inlineStr"/>
+      <c r="EH4" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
       <c r="EI4" t="inlineStr"/>
       <c r="EJ4" t="inlineStr"/>
       <c r="EK4" t="inlineStr"/>
       <c r="EL4" t="inlineStr"/>
       <c r="EM4" t="inlineStr"/>
-      <c r="EN4" t="inlineStr"/>
+      <c r="EN4" t="inlineStr">
+        <is>
+          <t>2#4</t>
+        </is>
+      </c>
       <c r="EO4" t="inlineStr"/>
       <c r="EP4" t="inlineStr"/>
       <c r="EQ4" t="inlineStr"/>
       <c r="ER4" t="inlineStr"/>
       <c r="ES4" t="inlineStr"/>
-      <c r="ET4" t="inlineStr"/>
+      <c r="ET4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2250,19 +2286,31 @@
           <t>10</t>
         </is>
       </c>
-      <c r="EH5" t="inlineStr"/>
+      <c r="EH5" t="inlineStr">
+        <is>
+          <t>DPD</t>
+        </is>
+      </c>
       <c r="EI5" t="inlineStr"/>
       <c r="EJ5" t="inlineStr"/>
       <c r="EK5" t="inlineStr"/>
       <c r="EL5" t="inlineStr"/>
       <c r="EM5" t="inlineStr"/>
-      <c r="EN5" t="inlineStr"/>
+      <c r="EN5" t="inlineStr">
+        <is>
+          <t>2#4</t>
+        </is>
+      </c>
       <c r="EO5" t="inlineStr"/>
       <c r="EP5" t="inlineStr"/>
       <c r="EQ5" t="inlineStr"/>
       <c r="ER5" t="inlineStr"/>
       <c r="ES5" t="inlineStr"/>
-      <c r="ET5" t="inlineStr"/>
+      <c r="ET5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
